--- a/Results/Figures.out/gbr_out_sheep_lon_fold_sets.xlsx
+++ b/Results/Figures.out/gbr_out_sheep_lon_fold_sets.xlsx
@@ -1,176 +1,172 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JHawkins\Documents\Github\DMI.prediction\R\Results\Figures.out\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_B89231272D09E89332D629AD3FBC059392594B1D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="48">
-  <si>
-    <t>train.t.IDs</t>
-  </si>
-  <si>
-    <t>train.t.IDs.length</t>
-  </si>
-  <si>
-    <t>test.t.IDs</t>
-  </si>
-  <si>
-    <t>train.t.IDs.length.1</t>
-  </si>
-  <si>
-    <t>t.ID.CCs</t>
-  </si>
-  <si>
-    <t>t.IDS.CCs.remaining</t>
-  </si>
-  <si>
-    <t>all.treatment.IDs</t>
-  </si>
-  <si>
-    <t>all.experiment.IDs</t>
-  </si>
-  <si>
-    <t>total.sample.size</t>
-  </si>
-  <si>
-    <t>c(108, 116, 136, 138, 141, 163, 164, 165, 166, 167, 180, 181, 182, 184, 192, 193, 194, 195, 196, 197, 198, 199, 200, 205, 209, 210, 211, 212)</t>
-  </si>
-  <si>
-    <t>c(107, 118, 134, 142, 183, 190, 191, 203, 208, 213)</t>
-  </si>
-  <si>
-    <t>c(107, 108, 116, 118, 134, 136, 138, 141, 142, 163, 164, 165, 166, 167, 180, 181, 182, 183, 184, 190, 191, 192, 193, 194, 195, 196, 197, 198, 199, 200, 203, 205, 208, 209, 210, 211, 212, 213)</t>
-  </si>
-  <si>
-    <t>c(27, 27, 29, 29, 33, 33, 33, 34, 34, 40, 40, 40, 40, 40, 44, 44, 44, 44, 44, 47, 47, 47, 47, 48, 48, 48, 48, 48, 48, 48, 49, 50, 51, 51, 51, 51, 51, 51)</t>
-  </si>
-  <si>
-    <t>c(107, 108, 116, 118, 134, 136, 138, 141, 142, 164, 181, 182, 183, 184, 190, 191, 192, 193, 194, 196, 198, 199, 203, 208, 209, 210, 211, 213)</t>
-  </si>
-  <si>
-    <t>c(163, 165, 166, 167, 180, 195, 197, 200, 205, 212)</t>
-  </si>
-  <si>
-    <t>c(107, 116, 118, 134, 138, 141, 142, 163, 165, 166, 167, 180, 181, 183, 184, 190, 191, 193, 194, 195, 197, 200, 203, 205, 208, 210, 212, 213)</t>
-  </si>
-  <si>
-    <t>c(108, 136, 164, 182, 192, 196, 198, 199, 209, 211)</t>
-  </si>
-  <si>
-    <t>c(108, 116, 136, 138, 141, 164, 181, 182, 184, 192, 193, 194, 196, 198, 199, 209, 210, 211)</t>
-  </si>
-  <si>
-    <t>c(107, 108, 118, 134, 136, 142, 163, 164, 165, 166, 167, 180, 182, 183, 190, 191, 192, 195, 196, 197, 198, 199, 200, 203, 205, 208, 209, 211, 212, 213)</t>
-  </si>
-  <si>
-    <t>c(116, 138, 141, 181, 184, 193, 194, 210)</t>
-  </si>
-  <si>
-    <t>c(107, 108, 116, 118, 134, 136, 138, 142, 163, 164, 166, 167, 182, 183, 190, 192, 193, 194, 196, 197, 198, 199, 203, 209, 210, 211, 212, 213)</t>
-  </si>
-  <si>
-    <t>c(141, 165, 180, 181, 184, 191, 195, 200, 205, 208)</t>
-  </si>
-  <si>
-    <t>c(107, 116, 141, 142, 164, 165, 166, 167, 180, 181, 183, 184, 191, 192, 193, 194, 195, 196, 197, 198, 199, 200, 203, 205, 208, 209, 210, 213)</t>
-  </si>
-  <si>
-    <t>c(108, 118, 134, 136, 138, 163, 182, 190, 211, 212)</t>
-  </si>
-  <si>
-    <t>c(108, 118, 134, 136, 138, 141, 142, 163, 165, 180, 181, 182, 184, 190, 191, 193, 194, 195, 198, 199, 200, 205, 208, 209, 210, 211, 212, 213)</t>
-  </si>
-  <si>
-    <t>c(107, 116, 164, 166, 167, 183, 192, 196, 197, 203)</t>
-  </si>
-  <si>
-    <t>c(107, 116, 142, 164, 166, 167, 183, 192, 193, 194, 196, 197, 198, 199, 203, 209, 210, 213)</t>
-  </si>
-  <si>
-    <t>c(107, 108, 116, 118, 134, 136, 138, 141, 163, 164, 165, 166, 167, 180, 181, 182, 183, 184, 190, 191, 192, 195, 196, 197, 200, 203, 205, 208, 211, 212)</t>
-  </si>
-  <si>
-    <t>c(142, 193, 194, 198, 199, 209, 210, 213)</t>
-  </si>
-  <si>
-    <t>c(107, 108, 116, 118, 134, 136, 138, 141, 142, 163, 164, 166, 167, 180, 182, 184, 190, 191, 194, 195, 198, 199, 200, 203, 205, 208, 210, 213)</t>
-  </si>
-  <si>
-    <t>c(165, 181, 183, 192, 193, 196, 197, 209, 211, 212)</t>
-  </si>
-  <si>
-    <t>c(108, 116, 134, 141, 142, 163, 165, 180, 181, 182, 183, 184, 190, 191, 192, 193, 195, 196, 197, 198, 199, 205, 208, 209, 210, 211, 212, 213)</t>
-  </si>
-  <si>
-    <t>c(107, 118, 136, 138, 164, 166, 167, 194, 200, 203)</t>
-  </si>
-  <si>
-    <t>c(107, 108, 118, 134, 136, 138, 164, 165, 166, 167, 180, 181, 182, 183, 190, 191, 192, 193, 194, 196, 197, 198, 200, 203, 208, 209, 211, 212)</t>
-  </si>
-  <si>
-    <t>c(116, 141, 142, 163, 184, 195, 199, 205, 210, 213)</t>
-  </si>
-  <si>
-    <t>c(108, 116, 134, 141, 142, 163, 180, 182, 184, 190, 191, 195, 198, 199, 205, 208, 210, 213)</t>
-  </si>
-  <si>
-    <t>c(107, 116, 118, 136, 138, 141, 142, 163, 164, 165, 166, 167, 181, 183, 184, 192, 193, 194, 195, 196, 197, 199, 200, 203, 205, 209, 210, 211, 212, 213)</t>
-  </si>
-  <si>
-    <t>c(108, 134, 180, 182, 190, 191, 198, 208)</t>
-  </si>
-  <si>
-    <t>c(107, 108, 191, 192, 193)</t>
-  </si>
-  <si>
-    <t>c(190, 203)</t>
-  </si>
-  <si>
-    <t>c(107, 108, 190, 191, 192, 193, 203)</t>
-  </si>
-  <si>
-    <t>c(107, 190, 192, 193, 203)</t>
-  </si>
-  <si>
-    <t>c(108, 191)</t>
-  </si>
-  <si>
-    <t>c(108, 190, 191, 193, 203)</t>
-  </si>
-  <si>
-    <t>c(107, 192)</t>
-  </si>
-  <si>
-    <t>c(107, 192, 193)</t>
-  </si>
-  <si>
-    <t>integer(0)</t>
-  </si>
-  <si>
-    <t>193</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
+  <si>
+    <t xml:space="preserve">train.t.IDs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train.t.IDs.length</t>
+  </si>
+  <si>
+    <t xml:space="preserve">test.t.IDs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train.t.IDs.length.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">t.ID.CCs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">t.IDS.CCs.remaining</t>
+  </si>
+  <si>
+    <t xml:space="preserve">all.treatment.IDs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">all.experiment.IDs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total.sample.size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(107, 108, 118, 136, 138, 141, 163, 164, 166, 167, 181, 183, 184, 190, 191, 193, 194, 195, 197, 198, 199, 200, 203, 205, 209, 210, 211, 212)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(116, 134, 142, 165, 180, 182, 192, 196, 208, 213)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(107, 108, 116, 118, 134, 136, 138, 141, 142, 163, 164, 165, 166, 167, 180, 181, 182, 183, 184, 190, 191, 192, 193, 194, 195, 196, 197, 198, 199, 200, 203, 205, 208, 209, 210, 211, 212, 213)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(27, 27, 29, 29, 33, 33, 33, 34, 34, 40, 40, 40, 40, 40, 44, 44, 44, 44, 44, 47, 47, 47, 47, 48, 48, 48, 48, 48, 48, 48, 49, 50, 51, 51, 51, 51, 51, 51)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(107, 116, 118, 134, 136, 138, 142, 164, 165, 166, 180, 181, 182, 183, 191, 192, 193, 196, 197, 198, 199, 200, 205, 208, 210, 211, 212, 213)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(108, 141, 163, 167, 184, 190, 194, 195, 203, 209)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(108, 116, 134, 141, 142, 163, 165, 166, 167, 180, 181, 182, 184, 190, 192, 193, 194, 195, 196, 197, 200, 203, 205, 208, 209, 210, 211, 213)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(107, 118, 136, 138, 164, 183, 191, 198, 199, 212)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(107, 118, 136, 138, 164, 166, 181, 183, 191, 193, 197, 198, 199, 200, 205, 210, 211, 212)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(107, 108, 116, 118, 134, 136, 138, 141, 142, 163, 164, 165, 167, 180, 182, 183, 184, 190, 191, 192, 194, 195, 196, 198, 199, 203, 208, 209, 212, 213)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(166, 181, 193, 197, 200, 205, 210, 211)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(108, 116, 118, 138, 142, 163, 164, 165, 166, 167, 180, 182, 183, 184, 190, 191, 192, 194, 196, 197, 199, 200, 203)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(107, 134, 136, 141, 181, 193, 195, 198)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(107, 108, 116, 118, 134, 136, 138, 141, 142, 163, 164, 165, 166, 167, 180, 181, 182, 183, 184, 190, 191, 192, 193, 194, 195, 196, 197, 198, 199, 200, 203)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(107, 108, 116, 134, 136, 138, 141, 163, 164, 165, 180, 181, 182, 183, 184, 191, 193, 195, 196, 197, 198, 199, 200)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(118, 142, 166, 167, 190, 192, 194, 203)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(107, 108, 116, 118, 134, 136, 141, 142, 165, 166, 167, 181, 183, 184, 190, 191, 192, 193, 194, 195, 198, 199, 203)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(138, 163, 164, 180, 182, 196, 197, 200)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(108, 116, 138, 163, 164, 165, 180, 182, 183, 184, 191, 196, 197, 199, 200)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(107, 118, 134, 136, 138, 141, 142, 163, 164, 166, 167, 180, 181, 182, 190, 192, 193, 194, 195, 196, 197, 198, 200, 203)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(108, 116, 165, 183, 184, 191, 199)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(107, 108, 116, 118, 136, 141, 163, 165, 166, 180, 181, 182, 183, 184, 190, 191, 193, 194, 195, 196, 198, 200, 203)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(134, 138, 142, 164, 167, 192, 197, 199)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(107, 108, 118, 134, 136, 138, 141, 142, 163, 164, 167, 183, 184, 191, 192, 194, 195, 196, 197, 198, 199, 200, 203)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(116, 165, 166, 180, 181, 182, 190, 193)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(107, 116, 134, 138, 142, 164, 165, 166, 167, 180, 181, 182, 183, 184, 190, 191, 192, 193, 195, 197, 198, 199, 203)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(108, 118, 136, 141, 163, 194, 196, 200)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(107, 108, 118, 136, 141, 163, 183, 184, 191, 194, 195, 196, 198, 200, 203)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(108, 116, 118, 134, 136, 138, 141, 142, 163, 164, 165, 166, 167, 180, 181, 182, 190, 192, 193, 194, 196, 197, 199, 200)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(107, 183, 184, 191, 195, 198, 203)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(107, 108, 118, 134, 138, 141, 142, 163, 164, 165, 180, 183, 184, 190, 191, 192, 193, 195, 196, 197, 198, 199, 203, 205, 208, 210, 213)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(116, 136, 166, 167, 181, 182, 194, 200, 211)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(107, 108, 116, 118, 134, 136, 138, 141, 142, 163, 164, 165, 166, 167, 180, 181, 182, 183, 184, 190, 191, 192, 193, 194, 195, 196, 197, 198, 199, 200, 203, 205, 208, 210, 211, 213)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(107, 108, 116, 118, 136, 138, 141, 142, 163, 166, 167, 181, 182, 184, 190, 193, 194, 195, 196, 197, 198, 199, 200, 203, 205, 211, 213)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(134, 164, 165, 180, 183, 191, 192, 208, 210)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(108, 116, 118, 134, 136, 141, 142, 164, 165, 166, 167, 180, 181, 182, 183, 191, 192, 194, 195, 196, 198, 199, 200, 208, 210, 211, 213)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(107, 138, 163, 184, 190, 193, 197, 203, 205)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(107, 108, 118, 138, 141, 142, 163, 184, 190, 193, 195, 196, 197, 198, 199, 203, 205, 213)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(107, 116, 134, 136, 138, 163, 164, 165, 166, 167, 180, 181, 182, 183, 184, 190, 191, 192, 193, 194, 197, 200, 203, 205, 208, 210, 211)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(108, 118, 141, 142, 195, 196, 198, 199, 213)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -206,15 +202,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -496,11 +483,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -529,17 +516,17 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="n">
         <v>10</v>
       </c>
       <c r="C2" t="s">
         <v>10</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>10</v>
       </c>
       <c r="E2" t="s">
@@ -554,21 +541,21 @@
       <c r="H2" t="s">
         <v>12</v>
       </c>
-      <c r="I2">
+      <c r="I2" t="n">
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="n">
         <v>10</v>
       </c>
       <c r="C3" t="s">
         <v>14</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="n">
         <v>10</v>
       </c>
       <c r="E3" t="s">
@@ -583,21 +570,21 @@
       <c r="H3" t="s">
         <v>12</v>
       </c>
-      <c r="I3">
+      <c r="I3" t="n">
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>15</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="n">
         <v>10</v>
       </c>
       <c r="C4" t="s">
         <v>16</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="n">
         <v>10</v>
       </c>
       <c r="E4" t="s">
@@ -612,21 +599,21 @@
       <c r="H4" t="s">
         <v>12</v>
       </c>
-      <c r="I4">
+      <c r="I4" t="n">
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>18</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="n">
         <v>8</v>
       </c>
       <c r="C5" t="s">
         <v>19</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="n">
         <v>8</v>
       </c>
       <c r="E5" t="s">
@@ -641,28 +628,28 @@
       <c r="H5" t="s">
         <v>12</v>
       </c>
-      <c r="I5">
+      <c r="I5" t="n">
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>20</v>
       </c>
-      <c r="B6">
-        <v>10</v>
+      <c r="B6" t="n">
+        <v>8</v>
       </c>
       <c r="C6" t="s">
         <v>21</v>
       </c>
-      <c r="D6">
-        <v>10</v>
+      <c r="D6" t="n">
+        <v>8</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="G6" t="s">
         <v>11</v>
@@ -670,25 +657,25 @@
       <c r="H6" t="s">
         <v>12</v>
       </c>
-      <c r="I6">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I6" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" t="n">
+        <v>8</v>
+      </c>
+      <c r="E7" t="s">
         <v>22</v>
-      </c>
-      <c r="B7">
-        <v>10</v>
-      </c>
-      <c r="C7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7">
-        <v>10</v>
-      </c>
-      <c r="E7" t="s">
-        <v>11</v>
       </c>
       <c r="F7" t="s">
         <v>20</v>
@@ -699,260 +686,260 @@
       <c r="H7" t="s">
         <v>12</v>
       </c>
-      <c r="I7">
+      <c r="I7" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" t="n">
+        <v>8</v>
+      </c>
+      <c r="C8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" t="n">
+        <v>7</v>
+      </c>
+      <c r="C9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I9" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" t="n">
+        <v>8</v>
+      </c>
+      <c r="E10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" t="s">
+        <v>12</v>
+      </c>
+      <c r="I10" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" t="n">
+        <v>8</v>
+      </c>
+      <c r="C11" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" t="n">
+        <v>8</v>
+      </c>
+      <c r="E11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G11" t="s">
+        <v>11</v>
+      </c>
+      <c r="H11" t="s">
+        <v>12</v>
+      </c>
+      <c r="I11" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" t="n">
+        <v>8</v>
+      </c>
+      <c r="C12" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" t="n">
+        <v>8</v>
+      </c>
+      <c r="E12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" t="s">
+        <v>36</v>
+      </c>
+      <c r="G12" t="s">
+        <v>11</v>
+      </c>
+      <c r="H12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I12" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" t="n">
+        <v>7</v>
+      </c>
+      <c r="C13" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8">
-        <v>10</v>
-      </c>
-      <c r="C8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8">
-        <v>10</v>
-      </c>
-      <c r="E8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" t="s">
-        <v>26</v>
-      </c>
-      <c r="G8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I8">
+      <c r="D13" t="n">
+        <v>7</v>
+      </c>
+      <c r="E13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9">
-        <v>8</v>
-      </c>
-      <c r="C9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9">
-        <v>8</v>
-      </c>
-      <c r="E9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" t="s">
-        <v>28</v>
-      </c>
-      <c r="G9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H9" t="s">
-        <v>12</v>
-      </c>
-      <c r="I9">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10">
-        <v>10</v>
-      </c>
-      <c r="C10" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10">
-        <v>10</v>
-      </c>
-      <c r="E10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10" t="s">
-        <v>11</v>
-      </c>
-      <c r="H10" t="s">
-        <v>12</v>
-      </c>
-      <c r="I10">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="G13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H13" t="s">
+        <v>12</v>
+      </c>
+      <c r="I13" t="n">
         <v>31</v>
       </c>
-      <c r="B11">
-        <v>10</v>
-      </c>
-      <c r="C11" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11">
-        <v>10</v>
-      </c>
-      <c r="E11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" t="s">
-        <v>29</v>
-      </c>
-      <c r="G11" t="s">
-        <v>11</v>
-      </c>
-      <c r="H11" t="s">
-        <v>12</v>
-      </c>
-      <c r="I11">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12">
-        <v>10</v>
-      </c>
-      <c r="C12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D12">
-        <v>10</v>
-      </c>
-      <c r="E12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" t="s">
-        <v>35</v>
-      </c>
-      <c r="G12" t="s">
-        <v>11</v>
-      </c>
-      <c r="H12" t="s">
-        <v>12</v>
-      </c>
-      <c r="I12">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" t="n">
+        <v>9</v>
+      </c>
+      <c r="C14" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14" t="n">
+        <v>9</v>
+      </c>
+      <c r="E14" t="s">
+        <v>41</v>
+      </c>
+      <c r="F14" t="s">
+        <v>41</v>
+      </c>
+      <c r="G14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H14" t="s">
+        <v>12</v>
+      </c>
+      <c r="I14" t="n">
         <v>36</v>
       </c>
-      <c r="B13">
-        <v>8</v>
-      </c>
-      <c r="C13" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13">
-        <v>8</v>
-      </c>
-      <c r="E13" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" t="s">
-        <v>37</v>
-      </c>
-      <c r="G13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H13" t="s">
-        <v>12</v>
-      </c>
-      <c r="I13">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14">
-        <v>2</v>
-      </c>
-      <c r="C14" t="s">
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" t="n">
+        <v>9</v>
+      </c>
+      <c r="C15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" t="n">
+        <v>9</v>
+      </c>
+      <c r="E15" t="s">
+        <v>41</v>
+      </c>
+      <c r="F15" t="s">
         <v>39</v>
       </c>
-      <c r="D14">
-        <v>2</v>
-      </c>
-      <c r="E14" t="s">
-        <v>40</v>
-      </c>
-      <c r="F14" t="s">
-        <v>40</v>
-      </c>
-      <c r="G14" t="s">
-        <v>11</v>
-      </c>
-      <c r="H14" t="s">
-        <v>12</v>
-      </c>
-      <c r="I14">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="G15" t="s">
+        <v>11</v>
+      </c>
+      <c r="H15" t="s">
+        <v>12</v>
+      </c>
+      <c r="I15" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" t="n">
+        <v>9</v>
+      </c>
+      <c r="C16" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" t="n">
+        <v>9</v>
+      </c>
+      <c r="E16" t="s">
         <v>41</v>
       </c>
-      <c r="B15">
-        <v>2</v>
-      </c>
-      <c r="C15" t="s">
-        <v>42</v>
-      </c>
-      <c r="D15">
-        <v>2</v>
-      </c>
-      <c r="E15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F15" t="s">
-        <v>38</v>
-      </c>
-      <c r="G15" t="s">
-        <v>11</v>
-      </c>
-      <c r="H15" t="s">
-        <v>12</v>
-      </c>
-      <c r="I15">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>43</v>
-      </c>
-      <c r="B16">
-        <v>2</v>
-      </c>
-      <c r="C16" t="s">
-        <v>44</v>
-      </c>
-      <c r="D16">
-        <v>2</v>
-      </c>
-      <c r="E16" t="s">
-        <v>40</v>
-      </c>
       <c r="F16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G16" t="s">
         <v>11</v>
@@ -960,28 +947,28 @@
       <c r="H16" t="s">
         <v>12</v>
       </c>
-      <c r="I16">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I16" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17" t="s">
-        <v>40</v>
-      </c>
-      <c r="B17">
-        <v>0</v>
+        <v>47</v>
+      </c>
+      <c r="B17" t="n">
+        <v>9</v>
       </c>
       <c r="C17" t="s">
-        <v>46</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
+        <v>48</v>
+      </c>
+      <c r="D17" t="n">
+        <v>9</v>
       </c>
       <c r="E17" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G17" t="s">
         <v>11</v>
@@ -989,12 +976,12 @@
       <c r="H17" t="s">
         <v>12</v>
       </c>
-      <c r="I17">
-        <v>7</v>
+      <c r="I17" t="n">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>